--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -131,12 +131,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -329,277 +333,336 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>2019</v>
+      <c r="A2" s="1" t="n">
+        <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>148</v>
+        <v>67.67</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>26</v>
+        <v>26.33</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>24</v>
+        <v>26.91</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>5</v>
+        <v>7.02</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>2</v>
+        <v>3.12</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>22</v>
+        <v>15.27</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>2020</v>
+      <c r="A3" s="1" t="n">
+        <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>174</v>
+        <v>67.42</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>30</v>
+        <v>31.71</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>25</v>
+        <v>21.23</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>9</v>
+        <v>2.72</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>11</v>
+        <v>11.13</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>28</v>
+        <v>15.9</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="I4" s="1" t="n">
+      <c r="B6" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <f aca="false">113.3-28.49-8.86-9.49</f>
+        <v>66.46</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="1" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>107.33</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>8.88</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>112.92</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>73.41</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="C6" s="1" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>108.07</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>145</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>183</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="G9" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" s="1" t="n">
+      <c r="H11" s="2" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -398,7 +398,7 @@
         <v>3.12</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>15.27</v>
+        <v>14.43</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
@@ -427,7 +427,7 @@
         <v>2.28</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>15.9</v>
+        <v>14.48</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>2.44</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2.89</v>
+        <v>21.77</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>0.16</v>
@@ -485,7 +485,7 @@
         <v>4.08</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31.68</v>
+        <v>28.24</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0.01</v>
@@ -514,7 +514,7 @@
         <v>5.36</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24.38</v>
+        <v>20.46</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0.08</v>
@@ -544,7 +544,7 @@
         <v>5.68</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>21.06</v>
+        <v>11.57</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -573,7 +573,8 @@
         <v>5.75</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.1</v>
+        <f aca="false">54.1-40.62</f>
+        <v>13.48</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0.86</v>
@@ -631,7 +632,7 @@
         <v>13.16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>36.53</v>
+        <v>11.86</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -660,7 +661,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>37.24</v>
+        <v>9.24</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -585,6 +585,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
+        <f aca="false">144.95-11.99-25.63</f>
         <v>107.33</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -603,7 +604,8 @@
         <v>8.88</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>37.49</v>
+        <f aca="false">37.49-25.63</f>
+        <v>11.86</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>3.7</v>
@@ -632,7 +634,8 @@
         <v>13.16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11.86</v>
+        <f aca="false">36.53-26.22</f>
+        <v>10.31</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -661,6 +664,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="2" t="n">
+        <f aca="false">37.24-28</f>
         <v>9.24</v>
       </c>
       <c r="I11" s="2" t="n">

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -380,25 +380,25 @@
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>67.67</v>
+        <v>67670</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>26.33</v>
+        <v>26330</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>26.91</v>
+        <v>26910</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>7.02</v>
+        <v>7020</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>11.93</v>
+        <v>11930</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3.12</v>
+        <v>3120</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.43</v>
+        <v>14430</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
@@ -409,25 +409,25 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>67.42</v>
+        <v>67420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>31.71</v>
+        <v>31710</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>21.23</v>
+        <v>21230</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.72</v>
+        <v>2720</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>11.13</v>
+        <v>11130</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2.28</v>
+        <v>2280</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>14.48</v>
+        <v>14480</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
@@ -438,28 +438,28 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>71.2</v>
+        <v>71200</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25.67</v>
+        <v>25670</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>23.6</v>
+        <v>23600</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.05</v>
+        <v>5050</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11.92</v>
+        <v>11920</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.44</v>
+        <v>2440</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21.77</v>
+        <v>21770</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.16</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -467,28 +467,28 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>83.19</v>
+        <v>83190</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30.46</v>
+        <v>30460</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>24.48</v>
+        <v>24480</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.39</v>
+        <v>9390</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>10.68</v>
+        <v>10680</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4.08</v>
+        <v>4080</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.24</v>
+        <v>28240</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,28 +496,28 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>82</v>
+        <v>82000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37.96</v>
+        <v>37960</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23.5</v>
+        <v>23500</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.49</v>
+        <v>1490</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.34</v>
+        <v>15340</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.36</v>
+        <v>5360</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20.46</v>
+        <v>20460</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.08</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -525,26 +525,25 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <f aca="false">113.3-28.49-8.86-9.49</f>
-        <v>66.46</v>
+        <v>66460</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31.81</v>
+        <v>31810</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23.08</v>
+        <v>23080</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.98</v>
+        <v>3980</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12.3</v>
+        <v>12300</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5.68</v>
+        <v>5680</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>11.57</v>
+        <v>11570</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -555,29 +554,28 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>86.72</v>
+        <v>86720</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>39.56</v>
+        <v>39560</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32.82</v>
+        <v>32820</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.91</v>
+        <v>5910</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.81</v>
+        <v>17810</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.75</v>
+        <v>5750</v>
       </c>
       <c r="H8" s="2" t="n">
-        <f aca="false">54.1-40.62</f>
-        <v>13.48</v>
+        <v>13480</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.86</v>
+        <v>860</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -585,30 +583,28 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">144.95-11.99-25.63</f>
-        <v>107.33</v>
+        <v>107330</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33.38</v>
+        <v>33380</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>58.39</v>
+        <v>58390</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20.06</v>
+        <v>20060</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26.77</v>
+        <v>26770</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8.88</v>
+        <v>8880</v>
       </c>
       <c r="H9" s="2" t="n">
-        <f aca="false">37.49-25.63</f>
-        <v>11.86</v>
+        <v>11860</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3.7</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -616,26 +612,25 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>112.92</v>
+        <v>112920</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>29.2</v>
+        <v>29200</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>73.41</v>
+        <v>73410</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.5</v>
+        <v>15500</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>41.81</v>
+        <v>41810</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13.16</v>
+        <v>13160</v>
       </c>
       <c r="H10" s="2" t="n">
-        <f aca="false">36.53-26.22</f>
-        <v>10.31</v>
+        <v>10310</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -646,26 +641,25 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>108.07</v>
+        <v>108070</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>30.83</v>
+        <v>30830</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>68</v>
+        <v>68000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14</v>
+        <v>14000</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>40</v>
+        <v>40000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12</v>
+        <v>12000</v>
       </c>
       <c r="H11" s="2" t="n">
-        <f aca="false">37.24-28</f>
-        <v>9.24</v>
+        <v>9240</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -380,25 +380,25 @@
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>67670</v>
+        <v>67670000</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>26330</v>
+        <v>26330000</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>26910</v>
+        <v>26910000</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>7020</v>
+        <v>7020000</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>11930</v>
+        <v>11930000</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3120</v>
+        <v>3120000</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14430</v>
+        <v>14430000</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
@@ -409,25 +409,25 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>67420</v>
+        <v>67420000</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>31710</v>
+        <v>31710000</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>21230</v>
+        <v>21230000</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2720</v>
+        <v>2720000</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>11130</v>
+        <v>11130000</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2280</v>
+        <v>2280000</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>14480</v>
+        <v>14480000</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
@@ -438,28 +438,28 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>71200</v>
+        <v>71200000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25670</v>
+        <v>25670000</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>23600</v>
+        <v>23600000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5050</v>
+        <v>5050000</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11920</v>
+        <v>11920000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2440</v>
+        <v>2440000</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21770</v>
+        <v>21770000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>160</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -467,28 +467,28 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>83190</v>
+        <v>83190000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30460</v>
+        <v>30460000</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>24480</v>
+        <v>24480000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9390</v>
+        <v>9390000</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>10680</v>
+        <v>10680000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4080</v>
+        <v>4080000</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28240</v>
+        <v>28240000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,28 +496,28 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>82000</v>
+        <v>82000000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37960</v>
+        <v>37960000</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23500</v>
+        <v>23500000</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1490</v>
+        <v>1490000</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15340</v>
+        <v>15340000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5360</v>
+        <v>5360000</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20460</v>
+        <v>20460000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -525,25 +525,25 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>66460</v>
+        <v>66460000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31810</v>
+        <v>31810000</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23080</v>
+        <v>23080000</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3980</v>
+        <v>3980000</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12300</v>
+        <v>12300000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5680</v>
+        <v>5680000</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>11570</v>
+        <v>11570000</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -554,28 +554,28 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>86720</v>
+        <v>86720000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>39560</v>
+        <v>39560000</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32820</v>
+        <v>32820000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5910</v>
+        <v>5910000</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17810</v>
+        <v>17810000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5750</v>
+        <v>5750000</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13480</v>
+        <v>13480000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>860</v>
+        <v>860000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -583,28 +583,28 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>107330</v>
+        <v>107330000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33380</v>
+        <v>33380000</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>58390</v>
+        <v>58390000</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20060</v>
+        <v>20060000</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26770</v>
+        <v>26770000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8880</v>
+        <v>8880000</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11860</v>
+        <v>11860000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3700</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -612,25 +612,25 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>112920</v>
+        <v>112920000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>29200</v>
+        <v>29200000</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>73410</v>
+        <v>73410000</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15500</v>
+        <v>15500000</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>41810</v>
+        <v>41810000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13160</v>
+        <v>13160000</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10310</v>
+        <v>10310000</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -641,25 +641,25 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>108070</v>
+        <v>108070000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>30830</v>
+        <v>30830000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>68000</v>
+        <v>68000000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14000</v>
+        <v>14000000</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>40000</v>
+        <v>40000000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12000</v>
+        <v>12000000</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9240</v>
+        <v>9240000</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -641,10 +641,11 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>108070000</v>
+        <f aca="false">182599473-46526494-28000000</f>
+        <v>108072979</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>30830000</v>
+        <v>30830499</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>68000000</v>
@@ -659,7 +660,8 @@
         <v>12000000</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9240000</v>
+        <f aca="false">37242480-28000000</f>
+        <v>9242480</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -20,33 +20,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Év</t>
   </si>
   <si>
-    <t xml:space="preserve">Összes bevétel (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Állami támogatás (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Közhatalmi bevétel (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iparűzési adó (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Építményadó (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telekadó (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Működési bevétel (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Átvett pénzeszközök (eFt)</t>
+    <t xml:space="preserve">Összes bevétel (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Állami támogatás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Közhatalmi bevétel (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iparűzési adó (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Építményadó (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telekadó (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Működési bevétel (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Átvett pénzeszközök (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idegenforgalmi adó (Ft)</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
@@ -344,6 +347,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -374,34 +378,42 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>67670000</v>
+        <f aca="false">121198591-11700000-839791-38457564-2530617</f>
+        <v>67670619</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>26330000</v>
+        <v>26334068</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>26910000</v>
+        <v>26910522</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>7020000</v>
+        <v>7015567</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>11930000</v>
+        <v>11933443</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3120000</v>
+        <v>3124487</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14430000</v>
+        <f aca="false">15265820-839791</f>
+        <v>14426029</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>282300</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -409,28 +421,33 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>67420000</v>
+        <f aca="false">110415338-0-41572048-1416102</f>
+        <v>67427188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>31710000</v>
+        <v>31711597</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>21230000</v>
+        <v>21231694</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2720000</v>
+        <v>2723241</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>11130000</v>
+        <v>11129718</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2280000</v>
+        <v>2280533</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>14480000</v>
+        <f aca="false">15899999-1416102</f>
+        <v>14483897</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>604700</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -438,28 +455,33 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>71200000</v>
+        <f aca="false">148322646-7500000-66501969-3120156</f>
+        <v>71200521</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25670000</v>
+        <v>25666036</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>23600000</v>
+        <v>23595151</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5050000</v>
+        <v>5046225</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11920000</v>
+        <v>11917136</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2440000</v>
+        <v>2436478</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21770000</v>
+        <f aca="false">24893363-3120156</f>
+        <v>21773207</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>160000</v>
+        <v>166127</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>224000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -467,28 +489,33 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>83190000</v>
+        <f aca="false">173957972-17999588-69331496-3440193</f>
+        <v>83186695</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30460000</v>
+        <v>30454735</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>24480000</v>
+        <v>24477156</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9390000</v>
+        <v>9395011</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>10680000</v>
+        <v>10682195</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4080000</v>
+        <v>4082881</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28240000</v>
+        <f aca="false">31680700-3440193</f>
+        <v>28240507</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1000</v>
+        <v>14297</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>83700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,28 +523,33 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>82000000</v>
+        <f aca="false">132957791-2500000-44528739-3920238</f>
+        <v>82008814</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37960000</v>
+        <v>37964077</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23500000</v>
+        <v>23504956</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1490000</v>
+        <v>1788921</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15340000</v>
+        <v>15337901</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5360000</v>
+        <v>5362346</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20460000</v>
+        <f aca="false">24382441-3920238</f>
+        <v>20462203</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8000</v>
+        <v>77578</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>493700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -525,28 +557,33 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>66460000</v>
+        <f aca="false">113284888-28487952-8858268-9488674</f>
+        <v>66449994</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31810000</v>
+        <v>31805701</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23080000</v>
+        <v>23076067</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3980000</v>
+        <v>3974820</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12300000</v>
+        <v>12601660</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5680000</v>
+        <v>5683552</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>11570000</v>
+        <f aca="false">21056900-9488674</f>
+        <v>11568226</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>636700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -554,28 +591,33 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>86720000</v>
+        <f aca="false">146142168-15374530-3427165-40615718</f>
+        <v>86724755</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>39560000</v>
+        <v>39555871</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32820000</v>
+        <v>32820032</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5910000</v>
+        <v>5903679</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17810000</v>
+        <v>19090971</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5750000</v>
+        <v>5912265</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13480000</v>
+        <f aca="false">54095370-40615718</f>
+        <v>13479652</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>860000</v>
+        <v>869200</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>931200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -583,28 +625,33 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>107330000</v>
+        <f aca="false">144940534-11986476-25629106</f>
+        <v>107324952</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33380000</v>
+        <v>33375164</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>58390000</v>
+        <v>58392183</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20060000</v>
+        <v>20065357</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26770000</v>
+        <v>26768278</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8880000</v>
+        <v>8879603</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11860000</v>
+        <f aca="false">37487833-25629106</f>
+        <v>11858727</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3700000</v>
+        <v>3698878</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2303479</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -612,28 +659,33 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>112920000</v>
+        <f aca="false">155024194-5692935-26216030-4606723-5594593</f>
+        <v>112913913</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>29200000</v>
+        <v>29198560</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>73410000</v>
+        <v>73405957</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15500000</v>
+        <v>15504583</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>41810000</v>
+        <v>41814896</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13160000</v>
+        <v>13162678</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10310000</v>
+        <f aca="false">36525426-26216030</f>
+        <v>10309396</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1983900</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -347,7 +347,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -378,7 +378,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -412,7 +412,7 @@
       <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>282300</v>
       </c>
     </row>
@@ -446,7 +446,7 @@
       <c r="I3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>604700</v>
       </c>
     </row>
@@ -480,7 +480,7 @@
       <c r="I4" s="2" t="n">
         <v>166127</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>224000</v>
       </c>
     </row>
@@ -514,7 +514,7 @@
       <c r="I5" s="2" t="n">
         <v>14297</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>83700</v>
       </c>
     </row>
@@ -548,7 +548,7 @@
       <c r="I6" s="2" t="n">
         <v>77578</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>493700</v>
       </c>
     </row>
@@ -582,7 +582,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>636700</v>
       </c>
     </row>
@@ -616,7 +616,7 @@
       <c r="I8" s="2" t="n">
         <v>869200</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>931200</v>
       </c>
     </row>
@@ -650,7 +650,7 @@
       <c r="I9" s="2" t="n">
         <v>3698878</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>2303479</v>
       </c>
     </row>
@@ -684,7 +684,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>1983900</v>
       </c>
     </row>
@@ -717,6 +717,9 @@
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1500000</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Év</t>
   </si>
@@ -50,6 +50,18 @@
   </si>
   <si>
     <t xml:space="preserve">Idegenforgalmi adó (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felhalmozási bevételek (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felhalmozási ÁHT (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saját vagyon értékesítése (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felhalmozási átvett pe (Ft)</t>
   </si>
 </sst>
 </file>
@@ -336,7 +348,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
@@ -348,6 +360,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="27.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -381,6 +397,18 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -415,6 +443,19 @@
       <c r="J2" s="1" t="n">
         <v>282300</v>
       </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">L2+M2+N2</f>
+        <v>52688181</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>38457564</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>2530617</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -449,6 +490,19 @@
       <c r="J3" s="1" t="n">
         <v>604700</v>
       </c>
+      <c r="K3" s="1" t="n">
+        <f aca="false">L3+M3+N3</f>
+        <v>53763606</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>12191558</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>41572048</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -483,6 +537,19 @@
       <c r="J4" s="1" t="n">
         <v>224000</v>
       </c>
+      <c r="K4" s="1" t="n">
+        <f aca="false">L4+M4+N4</f>
+        <v>74001969</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>66501969</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -517,6 +584,19 @@
       <c r="J5" s="1" t="n">
         <v>83700</v>
       </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">L5+M5+N5</f>
+        <v>87331084</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>17999588</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>69331496</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -551,6 +631,19 @@
       <c r="J6" s="1" t="n">
         <v>493700</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">L6+M6+N6</f>
+        <v>47028739</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>44528739</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -585,6 +678,19 @@
       <c r="J7" s="1" t="n">
         <v>636700</v>
       </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">L7+M7+N7</f>
+        <v>37346220</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>28487952</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>8858268</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -619,6 +725,19 @@
       <c r="J8" s="1" t="n">
         <v>931200</v>
       </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">L8+M8+N8</f>
+        <v>18801695</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>15374530</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>3427165</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -653,6 +772,19 @@
       <c r="J9" s="1" t="n">
         <v>2303479</v>
       </c>
+      <c r="K9" s="1" t="n">
+        <f aca="false">L9+M9+N9</f>
+        <v>11986476</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>11986476</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -687,6 +819,19 @@
       <c r="J10" s="1" t="n">
         <v>1983900</v>
       </c>
+      <c r="K10" s="1" t="n">
+        <f aca="false">L10+M10+N10</f>
+        <v>15894251</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>5692935</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>4606723</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>5594593</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -720,6 +865,19 @@
       </c>
       <c r="J11" s="1" t="n">
         <v>1500000</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <f aca="false">L11+M11+N11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -868,10 +868,10 @@
       </c>
       <c r="K11" s="1" t="n">
         <f aca="false">L11+M11+N11</f>
-        <v>0</v>
+        <v>46526494</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0</v>
+        <v>46526494</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>0</v>

--- a/public/data/bevetel.xlsx
+++ b/public/data/bevetel.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Év</t>
   </si>
   <si>
-    <t xml:space="preserve">Összes bevétel (Ft)</t>
+    <t xml:space="preserve">Összes működési bevétel (Ft)</t>
   </si>
   <si>
     <t xml:space="preserve">Állami támogatás (Ft)</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Működési bevétel (Ft)</t>
   </si>
   <si>
-    <t xml:space="preserve">Átvett pénzeszközök (Ft)</t>
+    <t xml:space="preserve">Működési átvett pe (Ft)</t>
   </si>
   <si>
     <t xml:space="preserve">Idegenforgalmi adó (Ft)</t>
@@ -352,18 +352,20 @@
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="27.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -744,7 +746,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">144940534-11986476-25629106</f>
+        <f aca="false">144940534-25629106-K9</f>
         <v>107324952</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -791,7 +793,7 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <f aca="false">155024194-5692935-26216030-4606723-5594593</f>
+        <f aca="false">149429601-26216030-K10</f>
         <v>112913913</v>
       </c>
       <c r="C10" s="2" t="n">
@@ -821,7 +823,7 @@
       </c>
       <c r="K10" s="1" t="n">
         <f aca="false">L10+M10+N10</f>
-        <v>15894251</v>
+        <v>10299658</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>5692935</v>
@@ -830,7 +832,7 @@
         <v>4606723</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>5594593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -838,7 +840,7 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <f aca="false">182599473-46526494-28000000</f>
+        <f aca="false">182599473-28000000-K11</f>
         <v>108072979</v>
       </c>
       <c r="C11" s="2" t="n">
